--- a/weeks/◆ 2026년 10월 3주 편성표 (1012 ~ 1018).xlsx
+++ b/weeks/◆ 2026년 10월 3주 편성표 (1012 ~ 1018).xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="37">
+  <fonts count="36">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -35,18 +35,6 @@
     <font>
       <name val="Arial"/>
       <sz val="10.0"/>
-      <color rgb="00333333"/>
-      <u val="none"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9.0"/>
-      <color rgb="00333333"/>
-      <u val="none"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9.0"/>
       <color rgb="00333333"/>
       <u val="none"/>
     </font>
@@ -242,6 +230,12 @@
       <color rgb="00333333"/>
       <u val="none"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9.0"/>
+      <color rgb="00333333"/>
+      <u val="none"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -277,12 +271,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEEEEE"/>
+        <fgColor rgb="00C1E1FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C1E1FF"/>
+        <fgColor rgb="00EEEEEE"/>
       </patternFill>
     </fill>
     <fill>
@@ -355,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true" applyNumberFormat="true">
       <alignment wrapText="true"/>
@@ -450,17 +444,17 @@
     <xf numFmtId="49" fontId="26" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="49" fontId="29" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyFont="true">
-      <alignment wrapText="true" horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="30" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="31" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
@@ -468,16 +462,13 @@
     <xf numFmtId="49" fontId="32" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="7" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyFont="true">
+      <alignment wrapText="true" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyFont="true">
-      <alignment wrapText="true" horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="35" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -582,7 +573,7 @@
       <c r="AK1" s="4"/>
       <c r="AL1" s="4" t="inlineStr">
         <is>
-          <t>1차 확정안입니다.</t>
+          <t>2차 확정안입니다.</t>
         </is>
       </c>
       <c r="AM1" s="4"/>
@@ -964,7 +955,7 @@
         </is>
       </c>
       <c r="Z8" s="25"/>
-      <c r="AA8" s="32" t="inlineStr">
+      <c r="AA8" s="29" t="inlineStr">
         <is>
           <t>05:20</t>
         </is>
@@ -974,19 +965,20 @@
           <t>55</t>
         </is>
       </c>
-      <c r="AC8" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="AC8" s="32" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="AD8" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AE8" s="33" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'리빙'</t>
+        </is>
+      </c>
+      <c r="AE8" s="30" t="inlineStr">
+        <is>
+          <t>나에노 세탁세제</t>
         </is>
       </c>
       <c r="AF8" s="25"/>
@@ -1085,7 +1077,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K9" s="34" t="inlineStr">
+      <c r="K9" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -1112,7 +1104,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="Q9" s="34" t="inlineStr">
+      <c r="Q9" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -1120,12 +1112,12 @@
       </c>
       <c r="R9" s="30" t="inlineStr">
         <is>
-          <t>'리빙'</t>
+          <t>'뷰티1'</t>
         </is>
       </c>
       <c r="S9" s="30" t="inlineStr">
         <is>
-          <t>욕실의여왕 탈취제</t>
+          <t>리더스 아이크림</t>
         </is>
       </c>
       <c r="T9" s="25"/>
@@ -1134,7 +1126,7 @@
           <t>06:15</t>
         </is>
       </c>
-      <c r="V9" s="35" t="inlineStr">
+      <c r="V9" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1149,7 +1141,7 @@
           <t>'패션2Lab'</t>
         </is>
       </c>
-      <c r="Y9" s="36" t="inlineStr">
+      <c r="Y9" s="34" t="inlineStr">
         <is>
           <t>에이앤디 퀼팅 자켓 1종</t>
         </is>
@@ -1165,7 +1157,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AC9" s="34" t="inlineStr">
+      <c r="AC9" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -1218,7 +1210,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="AO9" s="34" t="inlineStr">
+      <c r="AO9" s="32" t="inlineStr">
         <is>
           <t>수
 수</t>
@@ -1278,19 +1270,20 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K10" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="K10" s="32" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="L10" s="30" t="inlineStr">
         <is>
-          <t>'레포츠'</t>
+          <t>'주방'</t>
         </is>
       </c>
       <c r="M10" s="30" t="inlineStr">
         <is>
-          <t>팬암 26W 패딩 外</t>
+          <t>AM저압냄비</t>
         </is>
       </c>
       <c r="N10" s="25"/>
@@ -1304,7 +1297,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="Q10" s="34" t="inlineStr">
+      <c r="Q10" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -1326,7 +1319,7 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="V10" s="35" t="inlineStr">
+      <c r="V10" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1341,7 +1334,7 @@
           <t>'잡화'</t>
         </is>
       </c>
-      <c r="Y10" s="36" t="inlineStr">
+      <c r="Y10" s="34" t="inlineStr">
         <is>
           <t>스케쳐스 워킹화</t>
         </is>
@@ -1357,20 +1350,19 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AC10" s="34" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="AC10" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="AD10" s="30" t="inlineStr">
         <is>
-          <t>'주방'</t>
+          <t>'레포츠'</t>
         </is>
       </c>
       <c r="AE10" s="30" t="inlineStr">
         <is>
-          <t>AM저압냄비</t>
+          <t>팬암 26W 패딩 外</t>
         </is>
       </c>
       <c r="AF10" s="25"/>
@@ -1384,7 +1376,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AI10" s="34" t="inlineStr">
+      <c r="AI10" s="32" t="inlineStr">
         <is>
           <t>수
 수</t>
@@ -1444,7 +1436,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="E11" s="34" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -1492,7 +1484,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="P11" s="35" t="inlineStr">
+      <c r="P11" s="33" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -1507,7 +1499,7 @@
           <t>'패션1Lab'</t>
         </is>
       </c>
-      <c r="S11" s="37" t="inlineStr">
+      <c r="S11" s="35" t="inlineStr">
         <is>
           <t>프리마클라쎄 후드집업 재킷</t>
         </is>
@@ -1523,7 +1515,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="W11" s="34" t="inlineStr">
+      <c r="W11" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -1545,7 +1537,7 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="AB11" s="35" t="inlineStr">
+      <c r="AB11" s="33" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -1560,7 +1552,7 @@
           <t>'패션1Lab'</t>
         </is>
       </c>
-      <c r="AE11" s="36" t="inlineStr">
+      <c r="AE11" s="34" t="inlineStr">
         <is>
           <t>고비 캐시미어 로브</t>
         </is>
@@ -1571,7 +1563,7 @@
           <t>08:20</t>
         </is>
       </c>
-      <c r="AH11" s="35" t="inlineStr">
+      <c r="AH11" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1586,7 +1578,7 @@
           <t>P.D.Lab</t>
         </is>
       </c>
-      <c r="AK11" s="36" t="inlineStr">
+      <c r="AK11" s="34" t="inlineStr">
         <is>
           <t>브링크하우스 구스침구(26FW)</t>
         </is>
@@ -1602,7 +1594,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="AO11" s="34" t="inlineStr">
+      <c r="AO11" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
@@ -1683,7 +1675,7 @@
           <t>09:05</t>
         </is>
       </c>
-      <c r="P12" s="35" t="inlineStr">
+      <c r="P12" s="33" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -1698,7 +1690,7 @@
           <t>'패션4Lab'</t>
         </is>
       </c>
-      <c r="S12" s="37" t="inlineStr">
+      <c r="S12" s="35" t="inlineStr">
         <is>
           <t>어반어라운드 플리스 집업 1종</t>
         </is>
@@ -1714,29 +1706,28 @@
           <t>60</t>
         </is>
       </c>
-      <c r="W12" s="34" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="W12" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="X12" s="30" t="inlineStr">
         <is>
-          <t>'잡화'</t>
+          <t>'패션4Lab'</t>
         </is>
       </c>
       <c r="Y12" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">피플오브더월드 26FW </t>
+          <t>라우라비아조티 울블렌디드 팬츠 1종</t>
         </is>
       </c>
       <c r="Z12" s="25"/>
-      <c r="AA12" s="29" t="inlineStr">
+      <c r="AA12" s="36" t="inlineStr">
         <is>
           <t>09:05</t>
         </is>
       </c>
-      <c r="AB12" s="35" t="inlineStr">
+      <c r="AB12" s="33" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -1748,12 +1739,12 @@
       </c>
       <c r="AD12" s="30" t="inlineStr">
         <is>
-          <t>'패션4Lab'</t>
-        </is>
-      </c>
-      <c r="AE12" s="36" t="inlineStr">
-        <is>
-          <t>라우라비아조티 울블렌디드 팬츠 1종</t>
+          <t>Hit &amp; Best</t>
+        </is>
+      </c>
+      <c r="AE12" s="37" t="inlineStr">
+        <is>
+          <t>Hit &amp; Best</t>
         </is>
       </c>
       <c r="AF12" s="25"/>
@@ -1762,7 +1753,7 @@
           <t>09:20</t>
         </is>
       </c>
-      <c r="AH12" s="35" t="inlineStr">
+      <c r="AH12" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1777,7 +1768,7 @@
           <t>'건강식품1'</t>
         </is>
       </c>
-      <c r="AK12" s="36" t="inlineStr">
+      <c r="AK12" s="34" t="inlineStr">
         <is>
           <t>타이거모닝 진저샷</t>
         </is>
@@ -1826,7 +1817,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="E13" s="34" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -1843,7 +1834,7 @@
         </is>
       </c>
       <c r="H13" s="25"/>
-      <c r="I13" s="32" t="inlineStr">
+      <c r="I13" s="29" t="inlineStr">
         <is>
           <t>10:25</t>
         </is>
@@ -1853,19 +1844,20 @@
           <t>70</t>
         </is>
       </c>
-      <c r="K13" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
+      <c r="K13" s="32" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="L13" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="M13" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'패션2Lab'</t>
+        </is>
+      </c>
+      <c r="M13" s="30" t="inlineStr">
+        <is>
+          <t>이상봉 슬림시어 하이넥 블라우스 2종</t>
         </is>
       </c>
       <c r="N13" s="25"/>
@@ -1874,7 +1866,7 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="P13" s="35" t="inlineStr">
+      <c r="P13" s="33" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -1889,7 +1881,7 @@
           <t>'패션2Lab'</t>
         </is>
       </c>
-      <c r="S13" s="37" t="inlineStr">
+      <c r="S13" s="35" t="inlineStr">
         <is>
           <t>에바큐브 캐시미어 풀오버</t>
         </is>
@@ -1926,7 +1918,7 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="AB13" s="35" t="inlineStr">
+      <c r="AB13" s="33" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -1941,7 +1933,7 @@
           <t>언더웨어</t>
         </is>
       </c>
-      <c r="AE13" s="36" t="inlineStr">
+      <c r="AE13" s="34" t="inlineStr">
         <is>
           <t>로라애슐리 파자마 2세트</t>
         </is>
@@ -1952,7 +1944,7 @@
           <t>10:20</t>
         </is>
       </c>
-      <c r="AH13" s="35" t="inlineStr">
+      <c r="AH13" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1967,7 +1959,7 @@
           <t>'뷰티브랜드'</t>
         </is>
       </c>
-      <c r="AK13" s="36" t="inlineStr">
+      <c r="AK13" s="34" t="inlineStr">
         <is>
           <t>글러브인어보틀 쉴딩로션</t>
         </is>
@@ -2023,12 +2015,12 @@
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>'레포츠'</t>
+          <t>'주얼리'</t>
         </is>
       </c>
       <c r="G14" s="30" t="inlineStr">
         <is>
-          <t>아이그너 세일전</t>
+          <t>한국중앙금거래소 24K</t>
         </is>
       </c>
       <c r="H14" s="25"/>
@@ -2039,7 +2031,7 @@
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K14" s="24" t="inlineStr">
@@ -2068,7 +2060,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="Q14" s="34" t="inlineStr">
+      <c r="Q14" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -2090,7 +2082,7 @@
           <t>11:35</t>
         </is>
       </c>
-      <c r="V14" s="39" t="inlineStr">
+      <c r="V14" s="38" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -2105,9 +2097,9 @@
           <t>'패션4Lab'</t>
         </is>
       </c>
-      <c r="Y14" s="40" t="inlineStr">
-        <is>
-          <t>베네통 모크넥 2종 + 베스트</t>
+      <c r="Y14" s="39" t="inlineStr">
+        <is>
+          <t>정호진 트렌치코트</t>
         </is>
       </c>
       <c r="Z14" s="25"/>
@@ -2142,7 +2134,7 @@
           <t>11:20</t>
         </is>
       </c>
-      <c r="AH14" s="35" t="inlineStr">
+      <c r="AH14" s="33" t="inlineStr">
         <is>
           <t>85</t>
         </is>
@@ -2157,7 +2149,7 @@
           <t>'노블레스'</t>
         </is>
       </c>
-      <c r="AK14" s="36" t="inlineStr">
+      <c r="AK14" s="34" t="inlineStr">
         <is>
           <t>프라다_토트백</t>
         </is>
@@ -2173,7 +2165,7 @@
           <t>75</t>
         </is>
       </c>
-      <c r="AO14" s="34" t="inlineStr">
+      <c r="AO14" s="32" t="inlineStr">
         <is>
           <t>수
 수</t>
@@ -2204,7 +2196,7 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -2217,15 +2209,15 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="G15" s="41" t="inlineStr">
+      <c r="G15" s="40" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
       </c>
       <c r="H15" s="25"/>
-      <c r="I15" s="32" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="I15" s="29" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="J15" s="24" t="inlineStr">
@@ -2240,12 +2232,12 @@
       </c>
       <c r="L15" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="M15" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'패션1Lab'</t>
+        </is>
+      </c>
+      <c r="M15" s="30" t="inlineStr">
+        <is>
+          <t>누캐시미어 셔츠베스트</t>
         </is>
       </c>
       <c r="N15" s="25"/>
@@ -2259,7 +2251,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="Q15" s="34" t="inlineStr">
+      <c r="Q15" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
@@ -2281,7 +2273,7 @@
           <t>12:25</t>
         </is>
       </c>
-      <c r="V15" s="39" t="inlineStr">
+      <c r="V15" s="38" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -2296,9 +2288,9 @@
           <t>'패션2Lab'</t>
         </is>
       </c>
-      <c r="Y15" s="40" t="inlineStr">
-        <is>
-          <t>이상봉 슬림시어 하이넥 블라우스 2종</t>
+      <c r="Y15" s="39" t="inlineStr">
+        <is>
+          <t>이상봉 숄더백 라지</t>
         </is>
       </c>
       <c r="Z15" s="25"/>
@@ -2319,12 +2311,12 @@
       </c>
       <c r="AD15" s="30" t="inlineStr">
         <is>
-          <t>'패션1Lab'</t>
+          <t>'레포츠'</t>
         </is>
       </c>
       <c r="AE15" s="30" t="inlineStr">
         <is>
-          <t>누캐시미어 셔츠베스트</t>
+          <t>아이그너 세일전</t>
         </is>
       </c>
       <c r="AF15" s="25"/>
@@ -2333,7 +2325,7 @@
           <t>12:45</t>
         </is>
       </c>
-      <c r="AH15" s="35" t="inlineStr">
+      <c r="AH15" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -2348,7 +2340,7 @@
           <t>'노블레스'</t>
         </is>
       </c>
-      <c r="AK15" s="36" t="inlineStr">
+      <c r="AK15" s="34" t="inlineStr">
         <is>
           <t>구찌_크로스백</t>
         </is>
@@ -2364,7 +2356,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="AO15" s="34" t="inlineStr">
+      <c r="AO15" s="32" t="inlineStr">
         <is>
           <t>수
 수</t>
@@ -2388,14 +2380,14 @@
         </is>
       </c>
       <c r="B16" s="25"/>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>13:15</t>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -2405,23 +2397,23 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>'패션2Lab'</t>
-        </is>
-      </c>
-      <c r="G16" s="30" t="inlineStr">
-        <is>
-          <t>이상봉 숄더백 라지</t>
+          <t>Hit &amp; Best</t>
+        </is>
+      </c>
+      <c r="G16" s="37" t="inlineStr">
+        <is>
+          <t>Hit &amp; Best</t>
         </is>
       </c>
       <c r="H16" s="25"/>
       <c r="I16" s="29" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="J16" s="24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K16" s="24" t="inlineStr">
@@ -2434,7 +2426,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="M16" s="41" t="inlineStr">
+      <c r="M16" s="40" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -2450,7 +2442,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="Q16" s="34" t="inlineStr">
+      <c r="Q16" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -2472,12 +2464,12 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="V16" s="39" t="inlineStr">
+      <c r="V16" s="24" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="W16" s="34" t="inlineStr">
+      <c r="W16" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
@@ -2488,9 +2480,9 @@
           <t>'가전'</t>
         </is>
       </c>
-      <c r="Y16" s="40" t="inlineStr">
-        <is>
-          <t>LG 냉장고</t>
+      <c r="Y16" s="30" t="inlineStr">
+        <is>
+          <t>삼성 건조기</t>
         </is>
       </c>
       <c r="Z16" s="25"/>
@@ -2514,7 +2506,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="AE16" s="41" t="inlineStr">
+      <c r="AE16" s="40" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -2556,7 +2548,7 @@
           <t>75</t>
         </is>
       </c>
-      <c r="AO16" s="34" t="inlineStr">
+      <c r="AO16" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -2590,7 +2582,7 @@
           <t>55</t>
         </is>
       </c>
-      <c r="E17" s="34" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
@@ -2617,7 +2609,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="K17" s="34" t="inlineStr">
+      <c r="K17" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -2644,7 +2636,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="Q17" s="34" t="inlineStr">
+      <c r="Q17" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -2666,25 +2658,24 @@
           <t>14:05</t>
         </is>
       </c>
-      <c r="V17" s="39" t="inlineStr">
+      <c r="V17" s="24" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="W17" s="34" t="inlineStr">
-        <is>
-          <t>대
-수</t>
+      <c r="W17" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
         </is>
       </c>
       <c r="X17" s="30" t="inlineStr">
         <is>
-          <t>'가전'</t>
-        </is>
-      </c>
-      <c r="Y17" s="40" t="inlineStr">
-        <is>
-          <t>LG 건조기</t>
+          <t>'뷰티1'</t>
+        </is>
+      </c>
+      <c r="Y17" s="30" t="inlineStr">
+        <is>
+          <t>AHC 아이크림</t>
         </is>
       </c>
       <c r="Z17" s="25"/>
@@ -2698,7 +2689,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AC17" s="34" t="inlineStr">
+      <c r="AC17" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -2735,7 +2726,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="AK17" s="41" t="inlineStr">
+      <c r="AK17" s="40" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -2751,7 +2742,7 @@
           <t>65</t>
         </is>
       </c>
-      <c r="AO17" s="34" t="inlineStr">
+      <c r="AO17" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
@@ -2785,7 +2776,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -2798,7 +2789,7 @@
       </c>
       <c r="G18" s="30" t="inlineStr">
         <is>
-          <t>헤르젠 쌀냉장고</t>
+          <t>센스락진공밀폐용기</t>
         </is>
       </c>
       <c r="H18" s="25"/>
@@ -2807,12 +2798,12 @@
           <t>14:55</t>
         </is>
       </c>
-      <c r="J18" s="24" t="inlineStr">
+      <c r="J18" s="38" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="K18" s="34" t="inlineStr">
+      <c r="K18" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
@@ -2823,9 +2814,9 @@
           <t>'가전'</t>
         </is>
       </c>
-      <c r="M18" s="30" t="inlineStr">
-        <is>
-          <t>삼성 건조기</t>
+      <c r="M18" s="39" t="inlineStr">
+        <is>
+          <t>LG 냉장고</t>
         </is>
       </c>
       <c r="N18" s="25"/>
@@ -2865,47 +2856,46 @@
           <t>50</t>
         </is>
       </c>
-      <c r="W18" s="34" t="inlineStr">
-        <is>
-          <t>중
-수</t>
-        </is>
-      </c>
-      <c r="X18" s="30" t="inlineStr">
-        <is>
-          <t>'주방'</t>
-        </is>
-      </c>
-      <c r="Y18" s="30" t="inlineStr">
-        <is>
-          <t>에버홈 믹서기</t>
-        </is>
-      </c>
-      <c r="Z18" s="25"/>
-      <c r="AA18" s="29" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AB18" s="24" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AC18" s="34" t="inlineStr">
+      <c r="W18" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
         </is>
       </c>
+      <c r="X18" s="30" t="inlineStr">
+        <is>
+          <t>'주방'</t>
+        </is>
+      </c>
+      <c r="Y18" s="30" t="inlineStr">
+        <is>
+          <t>락앤락 온더테이블</t>
+        </is>
+      </c>
+      <c r="Z18" s="25"/>
+      <c r="AA18" s="36" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AB18" s="24" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AC18" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
       <c r="AD18" s="30" t="inlineStr">
         <is>
-          <t>'주방'</t>
-        </is>
-      </c>
-      <c r="AE18" s="30" t="inlineStr">
-        <is>
-          <t>락앤락 온더테이블</t>
+          <t>Hit &amp; Best</t>
+        </is>
+      </c>
+      <c r="AE18" s="37" t="inlineStr">
+        <is>
+          <t>Hit &amp; Best</t>
         </is>
       </c>
       <c r="AF18" s="25"/>
@@ -2945,7 +2935,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="AO18" s="34" t="inlineStr">
+      <c r="AO18" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -2989,7 +2979,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="G19" s="41" t="inlineStr">
+      <c r="G19" s="40" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -3000,24 +2990,25 @@
           <t>15:45</t>
         </is>
       </c>
-      <c r="J19" s="24" t="inlineStr">
+      <c r="J19" s="38" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="K19" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="K19" s="32" t="inlineStr">
+        <is>
+          <t>대
+수</t>
         </is>
       </c>
       <c r="L19" s="30" t="inlineStr">
         <is>
-          <t>'뷰티1'</t>
-        </is>
-      </c>
-      <c r="M19" s="30" t="inlineStr">
-        <is>
-          <t>AHC 아이크림</t>
+          <t>'가전'</t>
+        </is>
+      </c>
+      <c r="M19" s="39" t="inlineStr">
+        <is>
+          <t>LG 건조기</t>
         </is>
       </c>
       <c r="N19" s="25"/>
@@ -3083,7 +3074,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AC19" s="34" t="inlineStr">
+      <c r="AC19" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -3096,7 +3087,7 @@
       </c>
       <c r="AE19" s="30" t="inlineStr">
         <is>
-          <t>부가티 압력솥</t>
+          <t>헤르젠 쌀냉장고</t>
         </is>
       </c>
       <c r="AF19" s="25"/>
@@ -3131,12 +3122,12 @@
           <t>18:25</t>
         </is>
       </c>
-      <c r="AN19" s="35" t="inlineStr">
+      <c r="AN19" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AO19" s="34" t="inlineStr">
+      <c r="AO19" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
@@ -3147,7 +3138,7 @@
           <t>'해외여행'</t>
         </is>
       </c>
-      <c r="AQ19" s="37" t="inlineStr">
+      <c r="AQ19" s="35" t="inlineStr">
         <is>
           <t>참좋은여행 튀르키예</t>
         </is>
@@ -3165,7 +3156,7 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="D20" s="35" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -3180,7 +3171,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="G20" s="36" t="inlineStr">
+      <c r="G20" s="35" t="inlineStr">
         <is>
           <t>만능 국내산 보리새우</t>
         </is>
@@ -3248,7 +3239,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="W20" s="34" t="inlineStr">
+      <c r="W20" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -3301,7 +3292,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AI20" s="34" t="inlineStr">
+      <c r="AI20" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -3328,7 +3319,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AO20" s="34" t="inlineStr">
+      <c r="AO20" s="32" t="inlineStr">
         <is>
           <t>수
 수</t>
@@ -3357,7 +3348,7 @@
           <t>17:40</t>
         </is>
       </c>
-      <c r="D21" s="35" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -3372,7 +3363,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="G21" s="36" t="inlineStr">
+      <c r="G21" s="35" t="inlineStr">
         <is>
           <t>중앙해장 해장국세트</t>
         </is>
@@ -3409,7 +3400,7 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="P21" s="35" t="inlineStr">
+      <c r="P21" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -3424,7 +3415,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="S21" s="37" t="inlineStr">
+      <c r="S21" s="35" t="inlineStr">
         <is>
           <t>마니커 윙봉세트</t>
         </is>
@@ -3466,7 +3457,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AC21" s="34" t="inlineStr">
+      <c r="AC21" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -3488,12 +3479,12 @@
           <t>18:35</t>
         </is>
       </c>
-      <c r="AH21" s="35" t="inlineStr">
+      <c r="AH21" s="33" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AI21" s="34" t="inlineStr">
+      <c r="AI21" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
@@ -3504,7 +3495,7 @@
           <t>'해외여행'</t>
         </is>
       </c>
-      <c r="AK21" s="36" t="inlineStr">
+      <c r="AK21" s="34" t="inlineStr">
         <is>
           <t>교원투어 시즈오카</t>
         </is>
@@ -3520,7 +3511,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="AO21" s="34" t="inlineStr">
+      <c r="AO21" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -3554,7 +3545,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="E22" s="34" t="inlineStr">
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -3602,12 +3593,12 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="P22" s="35" t="inlineStr">
+      <c r="P22" s="24" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Q22" s="34" t="inlineStr">
+      <c r="Q22" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -3618,7 +3609,7 @@
           <t>'일반식품2'</t>
         </is>
       </c>
-      <c r="S22" s="37" t="inlineStr">
+      <c r="S22" s="30" t="inlineStr">
         <is>
           <t>돌체구스토 지니오s터치</t>
         </is>
@@ -3644,7 +3635,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="Y22" s="41" t="inlineStr">
+      <c r="Y22" s="40" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -3660,7 +3651,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AC22" s="34" t="inlineStr">
+      <c r="AC22" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -3687,7 +3678,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AI22" s="34" t="inlineStr">
+      <c r="AI22" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
@@ -3714,7 +3705,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="AO22" s="34" t="inlineStr">
+      <c r="AO22" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
@@ -3743,7 +3734,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="D23" s="35" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -3758,7 +3749,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="G23" s="36" t="inlineStr">
+      <c r="G23" s="35" t="inlineStr">
         <is>
           <t>그리팅 밸런스식 패키지</t>
         </is>
@@ -3769,7 +3760,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="J23" s="35" t="inlineStr">
+      <c r="J23" s="33" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -3784,7 +3775,7 @@
           <t>'액티브라이프'</t>
         </is>
       </c>
-      <c r="M23" s="37" t="inlineStr">
+      <c r="M23" s="35" t="inlineStr">
         <is>
           <t>마루킨 규슈낫또</t>
         </is>
@@ -3795,7 +3786,7 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="P23" s="35" t="inlineStr">
+      <c r="P23" s="33" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -3810,7 +3801,7 @@
           <t>'패션2Lab'</t>
         </is>
       </c>
-      <c r="S23" s="37" t="inlineStr">
+      <c r="S23" s="35" t="inlineStr">
         <is>
           <t>모라가 경량구스다운</t>
         </is>
@@ -3826,7 +3817,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="W23" s="34" t="inlineStr">
+      <c r="W23" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -3853,7 +3844,7 @@
           <t>75</t>
         </is>
       </c>
-      <c r="AC23" s="34" t="inlineStr">
+      <c r="AC23" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -3880,7 +3871,7 @@
           <t>65</t>
         </is>
       </c>
-      <c r="AI23" s="34" t="inlineStr">
+      <c r="AI23" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -3907,7 +3898,7 @@
           <t>65</t>
         </is>
       </c>
-      <c r="AO23" s="34" t="inlineStr">
+      <c r="AO23" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
@@ -3936,7 +3927,7 @@
           <t>20:10</t>
         </is>
       </c>
-      <c r="D24" s="35" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -3951,7 +3942,7 @@
           <t>멀티커머스</t>
         </is>
       </c>
-      <c r="G24" s="36" t="inlineStr">
+      <c r="G24" s="35" t="inlineStr">
         <is>
           <t>조니스그레놀라</t>
         </is>
@@ -3962,7 +3953,7 @@
           <t>20:05</t>
         </is>
       </c>
-      <c r="J24" s="35" t="inlineStr">
+      <c r="J24" s="33" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -3977,7 +3968,7 @@
           <t>'액티브라이프'</t>
         </is>
       </c>
-      <c r="M24" s="37" t="inlineStr">
+      <c r="M24" s="35" t="inlineStr">
         <is>
           <t>저스트레오 만능요리파우더</t>
         </is>
@@ -3988,7 +3979,7 @@
           <t>20:10</t>
         </is>
       </c>
-      <c r="P24" s="35" t="inlineStr">
+      <c r="P24" s="33" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -4003,7 +3994,7 @@
           <t>'패션1Lab'</t>
         </is>
       </c>
-      <c r="S24" s="37" t="inlineStr">
+      <c r="S24" s="35" t="inlineStr">
         <is>
           <t>올라카일리 토트백</t>
         </is>
@@ -4014,7 +4005,7 @@
           <t>20:45</t>
         </is>
       </c>
-      <c r="V24" s="35" t="inlineStr">
+      <c r="V24" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -4029,7 +4020,7 @@
           <t>'노블레스'</t>
         </is>
       </c>
-      <c r="Y24" s="36" t="inlineStr">
+      <c r="Y24" s="34" t="inlineStr">
         <is>
           <t>버버리_백팩</t>
         </is>
@@ -4045,39 +4036,39 @@
           <t>55</t>
         </is>
       </c>
-      <c r="AC24" s="34" t="inlineStr">
+      <c r="AC24" s="32" t="inlineStr">
+        <is>
+          <t>중
+수</t>
+        </is>
+      </c>
+      <c r="AD24" s="30" t="inlineStr">
+        <is>
+          <t>'주방'</t>
+        </is>
+      </c>
+      <c r="AE24" s="30" t="inlineStr">
+        <is>
+          <t>조이락 트라이탄 밀폐용기</t>
+        </is>
+      </c>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="29" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AI24" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
         </is>
       </c>
-      <c r="AD24" s="30" t="inlineStr">
-        <is>
-          <t>'뷰티1'</t>
-        </is>
-      </c>
-      <c r="AE24" s="30" t="inlineStr">
-        <is>
-          <t>달바 세럼</t>
-        </is>
-      </c>
-      <c r="AF24" s="25"/>
-      <c r="AG24" s="29" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="AH24" s="24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AI24" s="34" t="inlineStr">
-        <is>
-          <t>대
-수</t>
-        </is>
-      </c>
       <c r="AJ24" s="30" t="inlineStr">
         <is>
           <t>'해외여행'</t>
@@ -4101,17 +4092,17 @@
       </c>
       <c r="AO24" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="AP24" s="30" t="inlineStr">
         <is>
-          <t>'잡화'</t>
-        </is>
-      </c>
-      <c r="AQ24" s="30" t="inlineStr">
-        <is>
-          <t>베라왕 가방</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="AQ24" s="40" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4123,7 @@
           <t>65</t>
         </is>
       </c>
-      <c r="E25" s="34" t="inlineStr">
+      <c r="E25" s="32" t="inlineStr">
         <is>
           <t>수
 수</t>
@@ -4154,12 +4145,12 @@
           <t>20:45</t>
         </is>
       </c>
-      <c r="J25" s="35" t="inlineStr">
+      <c r="J25" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="K25" s="34" t="inlineStr">
+      <c r="K25" s="32" t="inlineStr">
         <is>
           <t>수
 수</t>
@@ -4170,7 +4161,7 @@
           <t>'건강식품1'</t>
         </is>
       </c>
-      <c r="M25" s="37" t="inlineStr">
+      <c r="M25" s="35" t="inlineStr">
         <is>
           <t>메리비 마누카허니콤</t>
         </is>
@@ -4181,7 +4172,7 @@
           <t>20:45</t>
         </is>
       </c>
-      <c r="P25" s="35" t="inlineStr">
+      <c r="P25" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -4196,7 +4187,7 @@
           <t>'뷰티2'</t>
         </is>
       </c>
-      <c r="S25" s="37" t="inlineStr">
+      <c r="S25" s="35" t="inlineStr">
         <is>
           <t>보로탈코 바디크림</t>
         </is>
@@ -4207,7 +4198,7 @@
           <t>21:45</t>
         </is>
       </c>
-      <c r="V25" s="35" t="inlineStr">
+      <c r="V25" s="33" t="inlineStr">
         <is>
           <t>70</t>
         </is>
@@ -4222,7 +4213,7 @@
           <t>'노블레스'</t>
         </is>
       </c>
-      <c r="Y25" s="36" t="inlineStr">
+      <c r="Y25" s="34" t="inlineStr">
         <is>
           <t>프라다_크로스백</t>
         </is>
@@ -4238,20 +4229,20 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AC25" s="34" t="inlineStr">
-        <is>
-          <t>중
+      <c r="AC25" s="32" t="inlineStr">
+        <is>
+          <t>대
 수</t>
         </is>
       </c>
       <c r="AD25" s="30" t="inlineStr">
         <is>
-          <t>'주방'</t>
+          <t>'뷰티1'</t>
         </is>
       </c>
       <c r="AE25" s="30" t="inlineStr">
         <is>
-          <t>조이락 트라이탄 밀폐용기</t>
+          <t>달바 세럼</t>
         </is>
       </c>
       <c r="AF25" s="25"/>
@@ -4260,7 +4251,7 @@
           <t>22:30</t>
         </is>
       </c>
-      <c r="AH25" s="35" t="inlineStr">
+      <c r="AH25" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -4275,7 +4266,7 @@
           <t>'뷰티브랜드'</t>
         </is>
       </c>
-      <c r="AK25" s="36" t="inlineStr">
+      <c r="AK25" s="34" t="inlineStr">
         <is>
           <t>[신]세인트프랑 링클샷 에센스</t>
         </is>
@@ -4324,7 +4315,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="E26" s="34" t="inlineStr">
+      <c r="E26" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -4341,7 +4332,7 @@
         </is>
       </c>
       <c r="H26" s="25"/>
-      <c r="I26" s="32" t="inlineStr">
+      <c r="I26" s="29" t="inlineStr">
         <is>
           <t>21:45</t>
         </is>
@@ -4353,17 +4344,17 @@
       </c>
       <c r="K26" s="24" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>대</t>
         </is>
       </c>
       <c r="L26" s="30" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="M26" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="M26" s="40" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="N26" s="25"/>
@@ -4403,19 +4394,20 @@
           <t>60</t>
         </is>
       </c>
-      <c r="W26" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="W26" s="32" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="X26" s="30" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="Y26" s="41" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'잡화'</t>
+        </is>
+      </c>
+      <c r="Y26" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">피플오브더월드 26FW </t>
         </is>
       </c>
       <c r="Z26" s="25"/>
@@ -4424,7 +4416,7 @@
           <t>22:40</t>
         </is>
       </c>
-      <c r="AB26" s="35" t="inlineStr">
+      <c r="AB26" s="33" t="inlineStr">
         <is>
           <t>115</t>
         </is>
@@ -4439,13 +4431,13 @@
           <t>'노블레스'</t>
         </is>
       </c>
-      <c r="AE26" s="36" t="inlineStr">
+      <c r="AE26" s="34" t="inlineStr">
         <is>
           <t>버버리_토트백</t>
         </is>
       </c>
       <c r="AF26" s="25"/>
-      <c r="AG26" s="29" t="inlineStr">
+      <c r="AG26" s="36" t="inlineStr">
         <is>
           <t>23:30</t>
         </is>
@@ -4462,12 +4454,12 @@
       </c>
       <c r="AJ26" s="30" t="inlineStr">
         <is>
-          <t>'패션4Lab'</t>
-        </is>
-      </c>
-      <c r="AK26" s="30" t="inlineStr">
-        <is>
-          <t>라일앤스캇 26FW 신상품 런칭</t>
+          <t>Hit &amp; Best</t>
+        </is>
+      </c>
+      <c r="AK26" s="37" t="inlineStr">
+        <is>
+          <t>Hit &amp; Best</t>
         </is>
       </c>
       <c r="AL26" s="25"/>
@@ -4524,7 +4516,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K27" s="34" t="inlineStr">
+      <c r="K27" s="32" t="inlineStr">
         <is>
           <t>대
 수</t>
@@ -4551,7 +4543,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="Q27" s="34" t="inlineStr">
+      <c r="Q27" s="32" t="inlineStr">
         <is>
           <t>중
 수</t>
@@ -4599,7 +4591,7 @@
           <t>00:35</t>
         </is>
       </c>
-      <c r="AB27" s="35" t="inlineStr">
+      <c r="AB27" s="33" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -4614,7 +4606,7 @@
           <t>'잡화'</t>
         </is>
       </c>
-      <c r="AE27" s="36" t="inlineStr">
+      <c r="AE27" s="34" t="inlineStr">
         <is>
           <t>MBB 핸드백</t>
         </is>
@@ -4640,7 +4632,7 @@
           <t>'GA'</t>
         </is>
       </c>
-      <c r="AK27" s="41" t="inlineStr">
+      <c r="AK27" s="40" t="inlineStr">
         <is>
           <t>#금융GA</t>
         </is>
@@ -4683,13 +4675,13 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="G28" s="41" t="inlineStr">
+      <c r="G28" s="40" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
       </c>
       <c r="H28" s="25"/>
-      <c r="I28" s="29" t="inlineStr">
+      <c r="I28" s="36" t="inlineStr">
         <is>
           <t>23:55</t>
         </is>
@@ -4701,21 +4693,21 @@
       </c>
       <c r="K28" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="L28" s="30" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="M28" s="41" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>Hit &amp; Best</t>
+        </is>
+      </c>
+      <c r="M28" s="37" t="inlineStr">
+        <is>
+          <t>Hit &amp; Best</t>
         </is>
       </c>
       <c r="N28" s="25"/>
-      <c r="O28" s="29" t="inlineStr">
+      <c r="O28" s="36" t="inlineStr">
         <is>
           <t>23:55</t>
         </is>
@@ -4732,12 +4724,12 @@
       </c>
       <c r="R28" s="30" t="inlineStr">
         <is>
-          <t>'국내여행'</t>
-        </is>
-      </c>
-      <c r="S28" s="30" t="inlineStr">
-        <is>
-          <t>용평리조트</t>
+          <t>Hit &amp; Best</t>
+        </is>
+      </c>
+      <c r="S28" s="37" t="inlineStr">
+        <is>
+          <t>Hit &amp; Best</t>
         </is>
       </c>
       <c r="T28" s="25"/>
